--- a/DATA/DGRAM Extranjerios_DocVigente_EdosvsPaises.xlsx
+++ b/DATA/DGRAM Extranjerios_DocVigente_EdosvsPaises.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bf48b3f04032ef9d/Documentos/SERVICIOS/PARKA/MIGRACIÓN/OFICINA/ALEX/IA-NAMI/BASES/DATA/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\furbina\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="8_{046D4E5B-03DE-4BC8-9E8C-033FCD420E13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E2C0EC1E-890B-4DBD-A460-BF029E71855E}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2621DCF9-2615-4E7A-98FE-39DF2B644C7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{034C1926-C401-45C5-9543-D3D2E70666A0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{034C1926-C401-45C5-9543-D3D2E70666A0}"/>
   </bookViews>
   <sheets>
-    <sheet name="EdosvsPais" sheetId="1" r:id="rId1"/>
+    <sheet name="EdosvsPais" sheetId="2" r:id="rId1"/>
   </sheets>
   <externalReferences>
     <externalReference r:id="rId2"/>
@@ -36,8 +36,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
@@ -275,7 +273,7 @@
     </font>
     <font>
       <b/>
-      <sz val="8"/>
+      <sz val="16"/>
       <color theme="1"/>
       <name val="Montserrat"/>
     </font>
@@ -713,7 +711,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Hoja2"/>
@@ -767,10 +765,14 @@
 </externalLink>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -808,7 +810,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -914,7 +916,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1056,43 +1058,43 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B2C6F54-5B0E-45D8-BF8D-B07FDA05B00D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F75E5FC-476B-437A-93A0-1D3AF108A039}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AC33"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="15.75" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="19.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="32.265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.265625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.86328125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="18.265625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="18" style="1" customWidth="1"/>
-    <col min="8" max="8" width="14.265625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="17.3984375" style="1" customWidth="1"/>
-    <col min="10" max="13" width="16.73046875" style="1" customWidth="1"/>
-    <col min="14" max="14" width="18.73046875" style="1" customWidth="1"/>
-    <col min="15" max="18" width="16.73046875" style="1" customWidth="1"/>
-    <col min="19" max="19" width="18.265625" style="1" customWidth="1"/>
-    <col min="20" max="24" width="16.73046875" style="1" customWidth="1"/>
-    <col min="25" max="25" width="12.1328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="19.59765625" style="1" customWidth="1"/>
-    <col min="27" max="27" width="14.265625" style="1" customWidth="1"/>
-    <col min="28" max="28" width="19.59765625" style="1" customWidth="1"/>
-    <col min="29" max="29" width="19" style="1" customWidth="1"/>
-    <col min="30" max="16384" width="11.3984375" style="1"/>
+    <col min="3" max="3" width="16.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.28515625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.85546875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="19" style="1" customWidth="1"/>
+    <col min="7" max="7" width="18.5703125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="13.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18" style="1" customWidth="1"/>
+    <col min="10" max="13" width="16.7109375" style="1" customWidth="1"/>
+    <col min="14" max="14" width="18.7109375" style="1" customWidth="1"/>
+    <col min="15" max="18" width="16.7109375" style="1" customWidth="1"/>
+    <col min="19" max="19" width="19.28515625" style="1" customWidth="1"/>
+    <col min="20" max="24" width="16.7109375" style="1" customWidth="1"/>
+    <col min="25" max="25" width="12.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="19.5703125" style="1" customWidth="1"/>
+    <col min="27" max="27" width="15" style="1" customWidth="1"/>
+    <col min="28" max="28" width="19.5703125" style="1" customWidth="1"/>
+    <col min="29" max="29" width="18.42578125" style="1" customWidth="1"/>
+    <col min="30" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="66.75" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:29" ht="75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="6" t="s">
         <v>60</v>
       </c>
@@ -1139,10 +1141,10 @@
         <v>13</v>
       </c>
       <c r="P1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="3" t="s">
         <v>14</v>
-      </c>
-      <c r="Q1" s="3" t="s">
-        <v>15</v>
       </c>
       <c r="R1" s="3" t="s">
         <v>16</v>
@@ -1181,42 +1183,42 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="4" t="s">
         <v>28</v>
       </c>
       <c r="B2" s="5">
-        <v>7748</v>
+        <v>7794</v>
       </c>
       <c r="C2" s="5">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="D2" s="5">
-        <v>7186</v>
+        <v>7230</v>
       </c>
       <c r="E2" s="5">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F2" s="5">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="G2" s="5">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="H2" s="5">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="I2" s="5">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="J2" s="5">
-        <v>663</v>
+        <v>669</v>
       </c>
       <c r="K2" s="5">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="L2" s="5">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="M2" s="5">
         <v>62</v>
@@ -1225,25 +1227,25 @@
         <v>188</v>
       </c>
       <c r="O2" s="5">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="P2" s="5">
+        <v>83</v>
+      </c>
+      <c r="Q2" s="5">
         <v>3</v>
       </c>
-      <c r="Q2" s="5">
-        <v>82</v>
-      </c>
       <c r="R2" s="5">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="S2" s="5">
         <v>36</v>
       </c>
       <c r="T2" s="5">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="U2" s="5">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="V2" s="5">
         <v>90</v>
@@ -1252,164 +1254,164 @@
         <v>174</v>
       </c>
       <c r="X2" s="5">
-        <v>1242</v>
+        <v>1247</v>
       </c>
       <c r="Y2" s="5">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Z2" s="5">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AA2" s="5">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AB2" s="5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AC2" s="5">
         <v>93</v>
       </c>
     </row>
-    <row r="3" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="4" t="s">
         <v>29</v>
       </c>
       <c r="B3" s="5">
-        <v>49248</v>
+        <v>49455</v>
       </c>
       <c r="C3" s="5">
-        <v>2438</v>
+        <v>2463</v>
       </c>
       <c r="D3" s="5">
-        <v>46810</v>
+        <v>46992</v>
       </c>
       <c r="E3" s="5">
-        <v>1790</v>
+        <v>1799</v>
       </c>
       <c r="F3" s="5">
-        <v>15174</v>
+        <v>15225</v>
       </c>
       <c r="G3" s="5">
-        <v>3717</v>
+        <v>3721</v>
       </c>
       <c r="H3" s="5">
-        <v>1447</v>
+        <v>1456</v>
       </c>
       <c r="I3" s="5">
-        <v>2075</v>
+        <v>2085</v>
       </c>
       <c r="J3" s="5">
-        <v>2251</v>
+        <v>2272</v>
       </c>
       <c r="K3" s="5">
-        <v>5507</v>
+        <v>5531</v>
       </c>
       <c r="L3" s="5">
-        <v>3176</v>
+        <v>3189</v>
       </c>
       <c r="M3" s="5">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="N3" s="5">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O3" s="5">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="P3" s="5">
+        <v>6401</v>
+      </c>
+      <c r="Q3" s="5">
         <v>15</v>
       </c>
-      <c r="Q3" s="5">
-        <v>6364</v>
-      </c>
       <c r="R3" s="5">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="S3" s="5">
-        <v>1137</v>
+        <v>1130</v>
       </c>
       <c r="T3" s="5">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="U3" s="5">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="V3" s="5">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="W3" s="5">
         <v>109</v>
       </c>
       <c r="X3" s="5">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Y3" s="5">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="Z3" s="5">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AA3" s="5">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="AB3" s="5">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="AC3" s="5">
         <v>432</v>
       </c>
     </row>
-    <row r="4" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="4" t="s">
         <v>30</v>
       </c>
       <c r="B4" s="5">
-        <v>32434</v>
+        <v>32504</v>
       </c>
       <c r="C4" s="5">
-        <v>1666</v>
+        <v>1675</v>
       </c>
       <c r="D4" s="5">
-        <v>30768</v>
+        <v>30829</v>
       </c>
       <c r="E4" s="5">
         <v>109</v>
       </c>
       <c r="F4" s="5">
-        <v>18684</v>
+        <v>18703</v>
       </c>
       <c r="G4" s="5">
         <v>100</v>
       </c>
       <c r="H4" s="5">
-        <v>788</v>
+        <v>796</v>
       </c>
       <c r="I4" s="5">
         <v>589</v>
       </c>
       <c r="J4" s="5">
-        <v>624</v>
+        <v>629</v>
       </c>
       <c r="K4" s="5">
-        <v>1879</v>
+        <v>1903</v>
       </c>
       <c r="L4" s="5">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="M4" s="5">
-        <v>5171</v>
+        <v>5170</v>
       </c>
       <c r="N4" s="5">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="O4" s="5">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="P4" s="5">
+        <v>6</v>
+      </c>
+      <c r="Q4" s="5">
         <v>8</v>
-      </c>
-      <c r="Q4" s="5">
-        <v>6</v>
       </c>
       <c r="R4" s="5">
         <v>93</v>
@@ -1424,63 +1426,63 @@
         <v>127</v>
       </c>
       <c r="V4" s="5">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="W4" s="5">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="X4" s="5">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="Y4" s="5">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="Z4" s="5">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="AA4" s="5">
         <v>86</v>
       </c>
       <c r="AB4" s="5">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AC4" s="5">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
-    <row r="5" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="4" t="s">
         <v>31</v>
       </c>
       <c r="B5" s="5">
-        <v>6634</v>
+        <v>6636</v>
       </c>
       <c r="C5" s="5">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D5" s="5">
-        <v>6224</v>
+        <v>6225</v>
       </c>
       <c r="E5" s="5">
-        <v>768</v>
+        <v>773</v>
       </c>
       <c r="F5" s="5">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="G5" s="5">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="H5" s="5">
-        <v>1209</v>
+        <v>1212</v>
       </c>
       <c r="I5" s="5">
         <v>1071</v>
       </c>
       <c r="J5" s="5">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="K5" s="5">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L5" s="5">
         <v>70</v>
@@ -1492,16 +1494,16 @@
         <v>76</v>
       </c>
       <c r="O5" s="5">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P5" s="5">
+        <v>210</v>
+      </c>
+      <c r="Q5" s="5">
         <v>18</v>
       </c>
-      <c r="Q5" s="5">
-        <v>214</v>
-      </c>
       <c r="R5" s="5">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="S5" s="5">
         <v>42</v>
@@ -1528,69 +1530,69 @@
         <v>18</v>
       </c>
       <c r="AA5" s="5">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AB5" s="5">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="AC5" s="5">
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="4" t="s">
         <v>32</v>
       </c>
       <c r="B6" s="5">
-        <v>412051</v>
+        <v>413034</v>
       </c>
       <c r="C6" s="5">
-        <v>4010</v>
+        <v>4028</v>
       </c>
       <c r="D6" s="5">
-        <v>408041</v>
+        <v>409006</v>
       </c>
       <c r="E6" s="5">
-        <v>297817</v>
+        <v>297725</v>
       </c>
       <c r="F6" s="5">
-        <v>676</v>
+        <v>684</v>
       </c>
       <c r="G6" s="5">
-        <v>45372</v>
+        <v>45430</v>
       </c>
       <c r="H6" s="5">
-        <v>21374</v>
+        <v>21836</v>
       </c>
       <c r="I6" s="5">
-        <v>2496</v>
+        <v>2619</v>
       </c>
       <c r="J6" s="5">
-        <v>1365</v>
+        <v>1384</v>
       </c>
       <c r="K6" s="5">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="L6" s="5">
-        <v>22627</v>
+        <v>22630</v>
       </c>
       <c r="M6" s="5">
         <v>175</v>
       </c>
       <c r="N6" s="5">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="O6" s="5">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="P6" s="5">
+        <v>10778</v>
+      </c>
+      <c r="Q6" s="5">
         <v>25</v>
       </c>
-      <c r="Q6" s="5">
-        <v>10394</v>
-      </c>
       <c r="R6" s="5">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="S6" s="5">
         <v>36</v>
@@ -1599,90 +1601,90 @@
         <v>135</v>
       </c>
       <c r="U6" s="5">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="V6" s="5">
         <v>182</v>
       </c>
       <c r="W6" s="5">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="X6" s="5">
         <v>76</v>
       </c>
       <c r="Y6" s="5">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="Z6" s="5">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AA6" s="5">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="AB6" s="5">
         <v>40</v>
       </c>
       <c r="AC6" s="5">
-        <v>2119</v>
+        <v>2123</v>
       </c>
     </row>
-    <row r="7" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="4" t="s">
         <v>33</v>
       </c>
       <c r="B7" s="5">
-        <v>11406</v>
+        <v>11475</v>
       </c>
       <c r="C7" s="5">
+        <v>1499</v>
+      </c>
+      <c r="D7" s="5">
+        <v>9976</v>
+      </c>
+      <c r="E7" s="5">
+        <v>315</v>
+      </c>
+      <c r="F7" s="5">
+        <v>1688</v>
+      </c>
+      <c r="G7" s="5">
+        <v>796</v>
+      </c>
+      <c r="H7" s="5">
+        <v>1174</v>
+      </c>
+      <c r="I7" s="5">
+        <v>995</v>
+      </c>
+      <c r="J7" s="5">
+        <v>970</v>
+      </c>
+      <c r="K7" s="5">
         <v>1476</v>
       </c>
-      <c r="D7" s="5">
-        <v>9930</v>
-      </c>
-      <c r="E7" s="5">
-        <v>314</v>
-      </c>
-      <c r="F7" s="5">
-        <v>1685</v>
-      </c>
-      <c r="G7" s="5">
-        <v>792</v>
-      </c>
-      <c r="H7" s="5">
-        <v>1168</v>
-      </c>
-      <c r="I7" s="5">
-        <v>992</v>
-      </c>
-      <c r="J7" s="5">
-        <v>958</v>
-      </c>
-      <c r="K7" s="5">
-        <v>1467</v>
-      </c>
       <c r="L7" s="5">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="M7" s="5">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="N7" s="5">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O7" s="5">
         <v>199</v>
       </c>
       <c r="P7" s="5">
+        <v>110</v>
+      </c>
+      <c r="Q7" s="5">
         <v>14</v>
       </c>
-      <c r="Q7" s="5">
-        <v>110</v>
-      </c>
       <c r="R7" s="5">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="S7" s="5">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="T7" s="5">
         <v>70</v>
@@ -1694,19 +1696,19 @@
         <v>82</v>
       </c>
       <c r="W7" s="5">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="X7" s="5">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="Y7" s="5">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="Z7" s="5">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="AA7" s="5">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AB7" s="5">
         <v>33</v>
@@ -1715,152 +1717,152 @@
         <v>102</v>
       </c>
     </row>
-    <row r="8" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="4" t="s">
         <v>34</v>
       </c>
       <c r="B8" s="5">
-        <v>187529</v>
+        <v>189304</v>
       </c>
       <c r="C8" s="5">
-        <v>19549</v>
+        <v>19709</v>
       </c>
       <c r="D8" s="5">
-        <v>167980</v>
+        <v>169595</v>
       </c>
       <c r="E8" s="5">
-        <v>2408</v>
+        <v>2431</v>
       </c>
       <c r="F8" s="5">
-        <v>11675</v>
+        <v>11974</v>
       </c>
       <c r="G8" s="5">
-        <v>2862</v>
+        <v>2880</v>
       </c>
       <c r="H8" s="5">
-        <v>13555</v>
+        <v>13779</v>
       </c>
       <c r="I8" s="5">
-        <v>26475</v>
+        <v>26569</v>
       </c>
       <c r="J8" s="5">
-        <v>22643</v>
+        <v>22812</v>
       </c>
       <c r="K8" s="5">
-        <v>20265</v>
+        <v>20517</v>
       </c>
       <c r="L8" s="5">
-        <v>2467</v>
+        <v>2479</v>
       </c>
       <c r="M8" s="5">
-        <v>1511</v>
+        <v>1526</v>
       </c>
       <c r="N8" s="5">
-        <v>10982</v>
+        <v>11032</v>
       </c>
       <c r="O8" s="5">
-        <v>11861</v>
+        <v>11941</v>
       </c>
       <c r="P8" s="5">
-        <v>97</v>
+        <v>3555</v>
       </c>
       <c r="Q8" s="5">
-        <v>3503</v>
+        <v>98</v>
       </c>
       <c r="R8" s="5">
-        <v>5939</v>
+        <v>5969</v>
       </c>
       <c r="S8" s="5">
-        <v>2863</v>
+        <v>2872</v>
       </c>
       <c r="T8" s="5">
-        <v>4751</v>
+        <v>4811</v>
       </c>
       <c r="U8" s="5">
-        <v>4391</v>
+        <v>4423</v>
       </c>
       <c r="V8" s="5">
-        <v>2735</v>
+        <v>2757</v>
       </c>
       <c r="W8" s="5">
-        <v>2480</v>
+        <v>2505</v>
       </c>
       <c r="X8" s="5">
-        <v>2662</v>
+        <v>2675</v>
       </c>
       <c r="Y8" s="5">
-        <v>3434</v>
+        <v>3465</v>
       </c>
       <c r="Z8" s="5">
-        <v>2393</v>
+        <v>2437</v>
       </c>
       <c r="AA8" s="5">
-        <v>2710</v>
+        <v>2756</v>
       </c>
       <c r="AB8" s="5">
-        <v>2228</v>
+        <v>2239</v>
       </c>
       <c r="AC8" s="5">
-        <v>1090</v>
+        <v>1093</v>
       </c>
     </row>
-    <row r="9" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="4" t="s">
         <v>35</v>
       </c>
       <c r="B9" s="5">
-        <v>15776</v>
+        <v>15842</v>
       </c>
       <c r="C9" s="5">
-        <v>897</v>
+        <v>901</v>
       </c>
       <c r="D9" s="5">
-        <v>14879</v>
+        <v>14941</v>
       </c>
       <c r="E9" s="5">
         <v>463</v>
       </c>
       <c r="F9" s="5">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G9" s="5">
-        <v>3832</v>
+        <v>3837</v>
       </c>
       <c r="H9" s="5">
-        <v>1020</v>
+        <v>1027</v>
       </c>
       <c r="I9" s="5">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="J9" s="5">
-        <v>811</v>
+        <v>817</v>
       </c>
       <c r="K9" s="5">
-        <v>1888</v>
+        <v>1901</v>
       </c>
       <c r="L9" s="5">
-        <v>1391</v>
+        <v>1392</v>
       </c>
       <c r="M9" s="5">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="N9" s="5">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="O9" s="5">
         <v>277</v>
       </c>
       <c r="P9" s="5">
+        <v>122</v>
+      </c>
+      <c r="Q9" s="5">
         <v>2</v>
-      </c>
-      <c r="Q9" s="5">
-        <v>121</v>
       </c>
       <c r="R9" s="5">
         <v>429</v>
       </c>
       <c r="S9" s="5">
-        <v>824</v>
+        <v>833</v>
       </c>
       <c r="T9" s="5">
         <v>107</v>
@@ -1869,48 +1871,48 @@
         <v>143</v>
       </c>
       <c r="V9" s="5">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="W9" s="5">
         <v>99</v>
       </c>
       <c r="X9" s="5">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Y9" s="5">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Z9" s="5">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="AA9" s="5">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AB9" s="5">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="AC9" s="5">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
-    <row r="10" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="4" t="s">
         <v>36</v>
       </c>
       <c r="B10" s="5">
-        <v>3680</v>
+        <v>3681</v>
       </c>
       <c r="C10" s="5">
         <v>288</v>
       </c>
       <c r="D10" s="5">
-        <v>3392</v>
+        <v>3393</v>
       </c>
       <c r="E10" s="5">
         <v>79</v>
       </c>
       <c r="F10" s="5">
-        <v>986</v>
+        <v>990</v>
       </c>
       <c r="G10" s="5">
         <v>69</v>
@@ -1922,7 +1924,7 @@
         <v>232</v>
       </c>
       <c r="J10" s="5">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="K10" s="5">
         <v>166</v>
@@ -1931,19 +1933,19 @@
         <v>91</v>
       </c>
       <c r="M10" s="5">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="N10" s="5">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="O10" s="5">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="P10" s="5">
+        <v>47</v>
+      </c>
+      <c r="Q10" s="5">
         <v>4</v>
-      </c>
-      <c r="Q10" s="5">
-        <v>52</v>
       </c>
       <c r="R10" s="5">
         <v>22</v>
@@ -1973,7 +1975,7 @@
         <v>4</v>
       </c>
       <c r="AA10" s="5">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AB10" s="5">
         <v>8</v>
@@ -1982,18 +1984,18 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="4" t="s">
         <v>37</v>
       </c>
       <c r="B11" s="5">
-        <v>2523</v>
+        <v>2517</v>
       </c>
       <c r="C11" s="5">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D11" s="5">
-        <v>2301</v>
+        <v>2293</v>
       </c>
       <c r="E11" s="5">
         <v>60</v>
@@ -2002,7 +2004,7 @@
         <v>224</v>
       </c>
       <c r="G11" s="5">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="H11" s="5">
         <v>169</v>
@@ -2011,28 +2013,28 @@
         <v>175</v>
       </c>
       <c r="J11" s="5">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="K11" s="5">
-        <v>462</v>
+        <v>454</v>
       </c>
       <c r="L11" s="5">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M11" s="5">
         <v>31</v>
       </c>
       <c r="N11" s="5">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="O11" s="5">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="P11" s="5">
+        <v>16</v>
+      </c>
+      <c r="Q11" s="5">
         <v>1</v>
-      </c>
-      <c r="Q11" s="5">
-        <v>16</v>
       </c>
       <c r="R11" s="5">
         <v>28</v>
@@ -2050,10 +2052,10 @@
         <v>37</v>
       </c>
       <c r="W11" s="5">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="X11" s="5">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Y11" s="5">
         <v>69</v>
@@ -2071,60 +2073,60 @@
         <v>36</v>
       </c>
     </row>
-    <row r="12" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="4" t="s">
         <v>38</v>
       </c>
       <c r="B12" s="5">
-        <v>33747</v>
+        <v>34110</v>
       </c>
       <c r="C12" s="5">
-        <v>3462</v>
+        <v>3481</v>
       </c>
       <c r="D12" s="5">
-        <v>30285</v>
+        <v>30629</v>
       </c>
       <c r="E12" s="5">
-        <v>840</v>
+        <v>848</v>
       </c>
       <c r="F12" s="5">
-        <v>1319</v>
+        <v>1323</v>
       </c>
       <c r="G12" s="5">
-        <v>1445</v>
+        <v>1451</v>
       </c>
       <c r="H12" s="5">
-        <v>4016</v>
+        <v>4225</v>
       </c>
       <c r="I12" s="5">
-        <v>5069</v>
+        <v>5118</v>
       </c>
       <c r="J12" s="5">
-        <v>5372</v>
+        <v>5402</v>
       </c>
       <c r="K12" s="5">
-        <v>764</v>
+        <v>758</v>
       </c>
       <c r="L12" s="5">
-        <v>1176</v>
+        <v>1181</v>
       </c>
       <c r="M12" s="5">
         <v>207</v>
       </c>
       <c r="N12" s="5">
-        <v>1791</v>
+        <v>1795</v>
       </c>
       <c r="O12" s="5">
-        <v>1510</v>
+        <v>1507</v>
       </c>
       <c r="P12" s="5">
+        <v>952</v>
+      </c>
+      <c r="Q12" s="5">
         <v>23</v>
       </c>
-      <c r="Q12" s="5">
-        <v>941</v>
-      </c>
       <c r="R12" s="5">
-        <v>1023</v>
+        <v>1027</v>
       </c>
       <c r="S12" s="5">
         <v>300</v>
@@ -2133,105 +2135,105 @@
         <v>461</v>
       </c>
       <c r="U12" s="5">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="V12" s="5">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="W12" s="5">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="X12" s="5">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Y12" s="5">
-        <v>693</v>
+        <v>701</v>
       </c>
       <c r="Z12" s="5">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="AA12" s="5">
-        <v>508</v>
+        <v>516</v>
       </c>
       <c r="AB12" s="5">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="AC12" s="5">
         <v>369</v>
       </c>
     </row>
-    <row r="13" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="4" t="s">
         <v>39</v>
       </c>
       <c r="B13" s="5">
-        <v>28413</v>
+        <v>28483</v>
       </c>
       <c r="C13" s="5">
-        <v>2076</v>
+        <v>2084</v>
       </c>
       <c r="D13" s="5">
-        <v>26337</v>
+        <v>26399</v>
       </c>
       <c r="E13" s="5">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="F13" s="5">
-        <v>11084</v>
+        <v>11097</v>
       </c>
       <c r="G13" s="5">
-        <v>1291</v>
+        <v>1294</v>
       </c>
       <c r="H13" s="5">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="I13" s="5">
-        <v>1340</v>
+        <v>1343</v>
       </c>
       <c r="J13" s="5">
-        <v>1704</v>
+        <v>1714</v>
       </c>
       <c r="K13" s="5">
-        <v>1253</v>
+        <v>1268</v>
       </c>
       <c r="L13" s="5">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="M13" s="5">
-        <v>1164</v>
+        <v>1156</v>
       </c>
       <c r="N13" s="5">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="O13" s="5">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="P13" s="5">
+        <v>185</v>
+      </c>
+      <c r="Q13" s="5">
         <v>13</v>
       </c>
-      <c r="Q13" s="5">
-        <v>185</v>
-      </c>
       <c r="R13" s="5">
-        <v>526</v>
+        <v>533</v>
       </c>
       <c r="S13" s="5">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="T13" s="5">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="U13" s="5">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="V13" s="5">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="W13" s="5">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="X13" s="5">
-        <v>2605</v>
+        <v>2622</v>
       </c>
       <c r="Y13" s="5">
         <v>197</v>
@@ -2240,66 +2242,66 @@
         <v>120</v>
       </c>
       <c r="AA13" s="5">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AB13" s="5">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="AC13" s="5">
         <v>109</v>
       </c>
     </row>
-    <row r="14" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="4" t="s">
         <v>40</v>
       </c>
       <c r="B14" s="5">
-        <v>5281</v>
+        <v>5289</v>
       </c>
       <c r="C14" s="5">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="D14" s="5">
-        <v>4810</v>
+        <v>4819</v>
       </c>
       <c r="E14" s="5">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F14" s="5">
-        <v>1591</v>
+        <v>1588</v>
       </c>
       <c r="G14" s="5">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H14" s="5">
-        <v>737</v>
+        <v>741</v>
       </c>
       <c r="I14" s="5">
         <v>165</v>
       </c>
       <c r="J14" s="5">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="K14" s="5">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L14" s="5">
         <v>99</v>
       </c>
       <c r="M14" s="5">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="N14" s="5">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="O14" s="5">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="P14" s="5">
+        <v>11</v>
+      </c>
+      <c r="Q14" s="5">
         <v>2</v>
-      </c>
-      <c r="Q14" s="5">
-        <v>11</v>
       </c>
       <c r="R14" s="5">
         <v>31</v>
@@ -2314,7 +2316,7 @@
         <v>68</v>
       </c>
       <c r="V14" s="5">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="W14" s="5">
         <v>93</v>
@@ -2338,39 +2340,39 @@
         <v>34</v>
       </c>
     </row>
-    <row r="15" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" s="4" t="s">
         <v>41</v>
       </c>
       <c r="B15" s="5">
-        <v>8074</v>
+        <v>8237</v>
       </c>
       <c r="C15" s="5">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="D15" s="5">
-        <v>7144</v>
+        <v>7298</v>
       </c>
       <c r="E15" s="5">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F15" s="5">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="G15" s="5">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="H15" s="5">
-        <v>1063</v>
+        <v>1168</v>
       </c>
       <c r="I15" s="5">
-        <v>887</v>
+        <v>908</v>
       </c>
       <c r="J15" s="5">
-        <v>1319</v>
+        <v>1329</v>
       </c>
       <c r="K15" s="5">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="L15" s="5">
         <v>244</v>
@@ -2379,46 +2381,46 @@
         <v>68</v>
       </c>
       <c r="N15" s="5">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O15" s="5">
+        <v>199</v>
+      </c>
+      <c r="P15" s="5">
+        <v>172</v>
+      </c>
+      <c r="Q15" s="5">
+        <v>7</v>
+      </c>
+      <c r="R15" s="5">
         <v>197</v>
       </c>
-      <c r="P15" s="5">
-        <v>7</v>
-      </c>
-      <c r="Q15" s="5">
-        <v>168</v>
-      </c>
-      <c r="R15" s="5">
-        <v>196</v>
-      </c>
       <c r="S15" s="5">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="T15" s="5">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="U15" s="5">
         <v>151</v>
       </c>
       <c r="V15" s="5">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="W15" s="5">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="X15" s="5">
         <v>22</v>
       </c>
       <c r="Y15" s="5">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="Z15" s="5">
         <v>59</v>
       </c>
       <c r="AA15" s="5">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AB15" s="5">
         <v>50</v>
@@ -2427,128 +2429,128 @@
         <v>75</v>
       </c>
     </row>
-    <row r="16" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A16" s="4" t="s">
         <v>42</v>
       </c>
       <c r="B16" s="5">
-        <v>68724</v>
+        <v>69011</v>
       </c>
       <c r="C16" s="5">
-        <v>5042</v>
+        <v>5071</v>
       </c>
       <c r="D16" s="5">
-        <v>63682</v>
+        <v>63940</v>
       </c>
       <c r="E16" s="5">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="F16" s="5">
-        <v>23122</v>
+        <v>23172</v>
       </c>
       <c r="G16" s="5">
-        <v>1950</v>
+        <v>1953</v>
       </c>
       <c r="H16" s="5">
-        <v>2412</v>
+        <v>2439</v>
       </c>
       <c r="I16" s="5">
-        <v>5188</v>
+        <v>5201</v>
       </c>
       <c r="J16" s="5">
-        <v>4855</v>
+        <v>4874</v>
       </c>
       <c r="K16" s="5">
-        <v>1694</v>
+        <v>1709</v>
       </c>
       <c r="L16" s="5">
-        <v>1638</v>
+        <v>1653</v>
       </c>
       <c r="M16" s="5">
-        <v>8396</v>
+        <v>8408</v>
       </c>
       <c r="N16" s="5">
-        <v>1518</v>
+        <v>1527</v>
       </c>
       <c r="O16" s="5">
-        <v>1625</v>
+        <v>1630</v>
       </c>
       <c r="P16" s="5">
+        <v>415</v>
+      </c>
+      <c r="Q16" s="5">
         <v>24</v>
       </c>
-      <c r="Q16" s="5">
-        <v>410</v>
-      </c>
       <c r="R16" s="5">
-        <v>817</v>
+        <v>822</v>
       </c>
       <c r="S16" s="5">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="T16" s="5">
-        <v>1042</v>
+        <v>1047</v>
       </c>
       <c r="U16" s="5">
-        <v>1067</v>
+        <v>1074</v>
       </c>
       <c r="V16" s="5">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="W16" s="5">
-        <v>821</v>
+        <v>826</v>
       </c>
       <c r="X16" s="5">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="Y16" s="5">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="Z16" s="5">
-        <v>2407</v>
+        <v>2453</v>
       </c>
       <c r="AA16" s="5">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="AB16" s="5">
-        <v>434</v>
+        <v>443</v>
       </c>
       <c r="AC16" s="5">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
-    <row r="17" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A17" s="4" t="s">
         <v>43</v>
       </c>
       <c r="B17" s="5">
-        <v>6296</v>
+        <v>6333</v>
       </c>
       <c r="C17" s="5">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="D17" s="5">
-        <v>5709</v>
+        <v>5742</v>
       </c>
       <c r="E17" s="5">
         <v>178</v>
       </c>
       <c r="F17" s="5">
-        <v>1180</v>
+        <v>1192</v>
       </c>
       <c r="G17" s="5">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H17" s="5">
-        <v>728</v>
+        <v>734</v>
       </c>
       <c r="I17" s="5">
         <v>524</v>
       </c>
       <c r="J17" s="5">
-        <v>1012</v>
+        <v>1019</v>
       </c>
       <c r="K17" s="5">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L17" s="5">
         <v>178</v>
@@ -2560,16 +2562,16 @@
         <v>184</v>
       </c>
       <c r="O17" s="5">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="P17" s="5">
+        <v>29</v>
+      </c>
+      <c r="Q17" s="5">
         <v>2</v>
       </c>
-      <c r="Q17" s="5">
-        <v>29</v>
-      </c>
       <c r="R17" s="5">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="S17" s="5">
         <v>12</v>
@@ -2578,7 +2580,7 @@
         <v>77</v>
       </c>
       <c r="U17" s="5">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="V17" s="5">
         <v>89</v>
@@ -2596,7 +2598,7 @@
         <v>31</v>
       </c>
       <c r="AA17" s="5">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AB17" s="5">
         <v>41</v>
@@ -2605,72 +2607,72 @@
         <v>46</v>
       </c>
     </row>
-    <row r="18" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A18" s="4" t="s">
         <v>44</v>
       </c>
       <c r="B18" s="5">
-        <v>7199</v>
+        <v>7258</v>
       </c>
       <c r="C18" s="5">
-        <v>1051</v>
+        <v>1064</v>
       </c>
       <c r="D18" s="5">
-        <v>6148</v>
+        <v>6194</v>
       </c>
       <c r="E18" s="5">
         <v>183</v>
       </c>
       <c r="F18" s="5">
-        <v>1061</v>
+        <v>1078</v>
       </c>
       <c r="G18" s="5">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H18" s="5">
-        <v>751</v>
+        <v>758</v>
       </c>
       <c r="I18" s="5">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="J18" s="5">
-        <v>753</v>
+        <v>758</v>
       </c>
       <c r="K18" s="5">
         <v>134</v>
       </c>
       <c r="L18" s="5">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M18" s="5">
         <v>164</v>
       </c>
       <c r="N18" s="5">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="O18" s="5">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="P18" s="5">
+        <v>78</v>
+      </c>
+      <c r="Q18" s="5">
         <v>6</v>
       </c>
-      <c r="Q18" s="5">
-        <v>78</v>
-      </c>
       <c r="R18" s="5">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="S18" s="5">
         <v>40</v>
       </c>
       <c r="T18" s="5">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="U18" s="5">
         <v>151</v>
       </c>
       <c r="V18" s="5">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="W18" s="5">
         <v>302</v>
@@ -2685,90 +2687,90 @@
         <v>71</v>
       </c>
       <c r="AA18" s="5">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="AB18" s="5">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AC18" s="5">
         <v>62</v>
       </c>
     </row>
-    <row r="19" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A19" s="4" t="s">
         <v>45</v>
       </c>
       <c r="B19" s="5">
-        <v>16268</v>
+        <v>16313</v>
       </c>
       <c r="C19" s="5">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="D19" s="5">
-        <v>15438</v>
+        <v>15482</v>
       </c>
       <c r="E19" s="5">
         <v>71</v>
       </c>
       <c r="F19" s="5">
-        <v>7042</v>
+        <v>7067</v>
       </c>
       <c r="G19" s="5">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H19" s="5">
-        <v>505</v>
+        <v>512</v>
       </c>
       <c r="I19" s="5">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="J19" s="5">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="K19" s="5">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L19" s="5">
         <v>99</v>
       </c>
       <c r="M19" s="5">
-        <v>5370</v>
+        <v>5382</v>
       </c>
       <c r="N19" s="5">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="O19" s="5">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="P19" s="5">
+        <v>15</v>
+      </c>
+      <c r="Q19" s="5">
         <v>2</v>
       </c>
-      <c r="Q19" s="5">
-        <v>15</v>
-      </c>
       <c r="R19" s="5">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="S19" s="5">
         <v>19</v>
       </c>
       <c r="T19" s="5">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="U19" s="5">
         <v>48</v>
       </c>
       <c r="V19" s="5">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="W19" s="5">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="X19" s="5">
         <v>28</v>
       </c>
       <c r="Y19" s="5">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="Z19" s="5">
         <v>11</v>
@@ -2777,152 +2779,152 @@
         <v>23</v>
       </c>
       <c r="AB19" s="5">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AC19" s="5">
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" s="4" t="s">
         <v>46</v>
       </c>
       <c r="B20" s="5">
-        <v>42678</v>
+        <v>43011</v>
       </c>
       <c r="C20" s="5">
-        <v>2972</v>
+        <v>3011</v>
       </c>
       <c r="D20" s="5">
-        <v>39706</v>
+        <v>40000</v>
       </c>
       <c r="E20" s="5">
-        <v>794</v>
+        <v>801</v>
       </c>
       <c r="F20" s="5">
-        <v>1463</v>
+        <v>1473</v>
       </c>
       <c r="G20" s="5">
-        <v>5670</v>
+        <v>5701</v>
       </c>
       <c r="H20" s="5">
-        <v>2077</v>
+        <v>2102</v>
       </c>
       <c r="I20" s="5">
-        <v>7491</v>
+        <v>7506</v>
       </c>
       <c r="J20" s="5">
-        <v>3626</v>
+        <v>3668</v>
       </c>
       <c r="K20" s="5">
-        <v>3052</v>
+        <v>3087</v>
       </c>
       <c r="L20" s="5">
-        <v>1927</v>
+        <v>1931</v>
       </c>
       <c r="M20" s="5">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N20" s="5">
-        <v>1599</v>
+        <v>1615</v>
       </c>
       <c r="O20" s="5">
-        <v>894</v>
+        <v>900</v>
       </c>
       <c r="P20" s="5">
+        <v>927</v>
+      </c>
+      <c r="Q20" s="5">
         <v>30</v>
       </c>
-      <c r="Q20" s="5">
-        <v>920</v>
-      </c>
       <c r="R20" s="5">
-        <v>1115</v>
+        <v>1123</v>
       </c>
       <c r="S20" s="5">
-        <v>3917</v>
+        <v>3968</v>
       </c>
       <c r="T20" s="5">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="U20" s="5">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="V20" s="5">
         <v>486</v>
       </c>
       <c r="W20" s="5">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="X20" s="5">
-        <v>779</v>
+        <v>793</v>
       </c>
       <c r="Y20" s="5">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="Z20" s="5">
-        <v>526</v>
+        <v>537</v>
       </c>
       <c r="AA20" s="5">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="AB20" s="5">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="AC20" s="5">
-        <v>417</v>
+        <v>424</v>
       </c>
     </row>
-    <row r="21" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A21" s="4" t="s">
         <v>47</v>
       </c>
       <c r="B21" s="5">
-        <v>11758</v>
+        <v>11795</v>
       </c>
       <c r="C21" s="5">
-        <v>1246</v>
+        <v>1249</v>
       </c>
       <c r="D21" s="5">
-        <v>10512</v>
+        <v>10546</v>
       </c>
       <c r="E21" s="5">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="F21" s="5">
-        <v>3401</v>
+        <v>3416</v>
       </c>
       <c r="G21" s="5">
         <v>662</v>
       </c>
       <c r="H21" s="5">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="I21" s="5">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="J21" s="5">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="K21" s="5">
         <v>213</v>
       </c>
       <c r="L21" s="5">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="M21" s="5">
-        <v>1601</v>
+        <v>1606</v>
       </c>
       <c r="N21" s="5">
         <v>349</v>
       </c>
       <c r="O21" s="5">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="P21" s="5">
+        <v>41</v>
+      </c>
+      <c r="Q21" s="5">
         <v>6</v>
-      </c>
-      <c r="Q21" s="5">
-        <v>41</v>
       </c>
       <c r="R21" s="5">
         <v>81</v>
@@ -2931,19 +2933,19 @@
         <v>17</v>
       </c>
       <c r="T21" s="5">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="U21" s="5">
         <v>166</v>
       </c>
       <c r="V21" s="5">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="W21" s="5">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="X21" s="5">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Y21" s="5">
         <v>85</v>
@@ -2961,253 +2963,253 @@
         <v>101</v>
       </c>
     </row>
-    <row r="22" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" s="4" t="s">
         <v>48</v>
       </c>
       <c r="B22" s="5">
-        <v>17699</v>
+        <v>17800</v>
       </c>
       <c r="C22" s="5">
-        <v>1922</v>
+        <v>1933</v>
       </c>
       <c r="D22" s="5">
-        <v>15777</v>
+        <v>15867</v>
       </c>
       <c r="E22" s="5">
         <v>490</v>
       </c>
       <c r="F22" s="5">
-        <v>1338</v>
+        <v>1347</v>
       </c>
       <c r="G22" s="5">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="H22" s="5">
-        <v>1181</v>
+        <v>1193</v>
       </c>
       <c r="I22" s="5">
-        <v>2517</v>
+        <v>2528</v>
       </c>
       <c r="J22" s="5">
-        <v>2387</v>
+        <v>2384</v>
       </c>
       <c r="K22" s="5">
-        <v>402</v>
+        <v>420</v>
       </c>
       <c r="L22" s="5">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="M22" s="5">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="N22" s="5">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="O22" s="5">
-        <v>1019</v>
+        <v>1027</v>
       </c>
       <c r="P22" s="5">
-        <v>11</v>
+        <v>82</v>
       </c>
       <c r="Q22" s="5">
-        <v>80</v>
+        <v>12</v>
       </c>
       <c r="R22" s="5">
         <v>442</v>
       </c>
       <c r="S22" s="5">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="T22" s="5">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="U22" s="5">
         <v>407</v>
       </c>
       <c r="V22" s="5">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="W22" s="5">
-        <v>1489</v>
+        <v>1497</v>
       </c>
       <c r="X22" s="5">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Y22" s="5">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Z22" s="5">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AA22" s="5">
         <v>209</v>
       </c>
       <c r="AB22" s="5">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AC22" s="5">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
-    <row r="23" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A23" s="4" t="s">
         <v>49</v>
       </c>
       <c r="B23" s="5">
-        <v>24058</v>
+        <v>24224</v>
       </c>
       <c r="C23" s="5">
-        <v>2264</v>
+        <v>2278</v>
       </c>
       <c r="D23" s="5">
-        <v>21794</v>
+        <v>21946</v>
       </c>
       <c r="E23" s="5">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F23" s="5">
-        <v>2529</v>
+        <v>2547</v>
       </c>
       <c r="G23" s="5">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="H23" s="5">
-        <v>1367</v>
+        <v>1379</v>
       </c>
       <c r="I23" s="5">
-        <v>3845</v>
+        <v>3863</v>
       </c>
       <c r="J23" s="5">
-        <v>2593</v>
+        <v>2611</v>
       </c>
       <c r="K23" s="5">
-        <v>747</v>
+        <v>759</v>
       </c>
       <c r="L23" s="5">
+        <v>419</v>
+      </c>
+      <c r="M23" s="5">
+        <v>550</v>
+      </c>
+      <c r="N23" s="5">
+        <v>706</v>
+      </c>
+      <c r="O23" s="5">
+        <v>1080</v>
+      </c>
+      <c r="P23" s="5">
+        <v>113</v>
+      </c>
+      <c r="Q23" s="5">
+        <v>11</v>
+      </c>
+      <c r="R23" s="5">
+        <v>671</v>
+      </c>
+      <c r="S23" s="5">
+        <v>1071</v>
+      </c>
+      <c r="T23" s="5">
+        <v>588</v>
+      </c>
+      <c r="U23" s="5">
         <v>416</v>
       </c>
-      <c r="M23" s="5">
-        <v>548</v>
-      </c>
-      <c r="N23" s="5">
-        <v>703</v>
-      </c>
-      <c r="O23" s="5">
-        <v>1077</v>
-      </c>
-      <c r="P23" s="5">
-        <v>11</v>
-      </c>
-      <c r="Q23" s="5">
-        <v>110</v>
-      </c>
-      <c r="R23" s="5">
-        <v>667</v>
-      </c>
-      <c r="S23" s="5">
-        <v>1064</v>
-      </c>
-      <c r="T23" s="5">
-        <v>589</v>
-      </c>
-      <c r="U23" s="5">
-        <v>411</v>
-      </c>
       <c r="V23" s="5">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="W23" s="5">
-        <v>752</v>
+        <v>760</v>
       </c>
       <c r="X23" s="5">
-        <v>1054</v>
+        <v>1062</v>
       </c>
       <c r="Y23" s="5">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Z23" s="5">
-        <v>1015</v>
+        <v>1039</v>
       </c>
       <c r="AA23" s="5">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AB23" s="5">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="AC23" s="5">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
-    <row r="24" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" s="4" t="s">
         <v>50</v>
       </c>
       <c r="B24" s="5">
-        <v>112573</v>
+        <v>113236</v>
       </c>
       <c r="C24" s="5">
-        <v>9256</v>
+        <v>9302</v>
       </c>
       <c r="D24" s="5">
-        <v>103317</v>
+        <v>103934</v>
       </c>
       <c r="E24" s="5">
-        <v>4622</v>
+        <v>4641</v>
       </c>
       <c r="F24" s="5">
-        <v>13101</v>
+        <v>13141</v>
       </c>
       <c r="G24" s="5">
-        <v>1753</v>
+        <v>1768</v>
       </c>
       <c r="H24" s="5">
-        <v>18068</v>
+        <v>18274</v>
       </c>
       <c r="I24" s="5">
-        <v>6185</v>
+        <v>6195</v>
       </c>
       <c r="J24" s="5">
-        <v>4068</v>
+        <v>4091</v>
       </c>
       <c r="K24" s="5">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="L24" s="5">
-        <v>769</v>
+        <v>773</v>
       </c>
       <c r="M24" s="5">
-        <v>6345</v>
+        <v>6359</v>
       </c>
       <c r="N24" s="5">
-        <v>6614</v>
+        <v>6634</v>
       </c>
       <c r="O24" s="5">
-        <v>3118</v>
+        <v>3129</v>
       </c>
       <c r="P24" s="5">
-        <v>24895</v>
+        <v>182</v>
       </c>
       <c r="Q24" s="5">
-        <v>180</v>
+        <v>25113</v>
       </c>
       <c r="R24" s="5">
-        <v>872</v>
+        <v>878</v>
       </c>
       <c r="S24" s="5">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T24" s="5">
-        <v>1882</v>
+        <v>1894</v>
       </c>
       <c r="U24" s="5">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="V24" s="5">
         <v>2913</v>
       </c>
       <c r="W24" s="5">
-        <v>1345</v>
+        <v>1354</v>
       </c>
       <c r="X24" s="5">
         <v>207</v>
@@ -3216,158 +3218,158 @@
         <v>702</v>
       </c>
       <c r="Z24" s="5">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="AA24" s="5">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AB24" s="5">
-        <v>3138</v>
+        <v>3146</v>
       </c>
       <c r="AC24" s="5">
         <v>220</v>
       </c>
     </row>
-    <row r="25" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" s="4" t="s">
         <v>51</v>
       </c>
       <c r="B25" s="5">
-        <v>11255</v>
+        <v>11300</v>
       </c>
       <c r="C25" s="5">
-        <v>744</v>
+        <v>752</v>
       </c>
       <c r="D25" s="5">
-        <v>10511</v>
+        <v>10548</v>
       </c>
       <c r="E25" s="5">
         <v>204</v>
       </c>
       <c r="F25" s="5">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="G25" s="5">
-        <v>1743</v>
+        <v>1746</v>
       </c>
       <c r="H25" s="5">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="I25" s="5">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="J25" s="5">
-        <v>2076</v>
+        <v>2080</v>
       </c>
       <c r="K25" s="5">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="L25" s="5">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="M25" s="5">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N25" s="5">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="O25" s="5">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="P25" s="5">
+        <v>322</v>
+      </c>
+      <c r="Q25" s="5">
         <v>3</v>
-      </c>
-      <c r="Q25" s="5">
-        <v>312</v>
       </c>
       <c r="R25" s="5">
         <v>265</v>
       </c>
       <c r="S25" s="5">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="T25" s="5">
         <v>202</v>
       </c>
       <c r="U25" s="5">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="V25" s="5">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="W25" s="5">
-        <v>521</v>
+        <v>528</v>
       </c>
       <c r="X25" s="5">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="Y25" s="5">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="Z25" s="5">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AA25" s="5">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="AB25" s="5">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AC25" s="5">
         <v>130</v>
       </c>
     </row>
-    <row r="26" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A26" s="4" t="s">
         <v>52</v>
       </c>
       <c r="B26" s="5">
-        <v>10460</v>
+        <v>10470</v>
       </c>
       <c r="C26" s="5">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="D26" s="5">
-        <v>9666</v>
+        <v>9673</v>
       </c>
       <c r="E26" s="5">
         <v>142</v>
       </c>
       <c r="F26" s="5">
-        <v>3807</v>
+        <v>3808</v>
       </c>
       <c r="G26" s="5">
         <v>141</v>
       </c>
       <c r="H26" s="5">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="I26" s="5">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="J26" s="5">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="K26" s="5">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="L26" s="5">
         <v>116</v>
       </c>
       <c r="M26" s="5">
-        <v>2182</v>
+        <v>2184</v>
       </c>
       <c r="N26" s="5">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="O26" s="5">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="P26" s="5">
+        <v>12</v>
+      </c>
+      <c r="Q26" s="5">
         <v>2</v>
-      </c>
-      <c r="Q26" s="5">
-        <v>12</v>
       </c>
       <c r="R26" s="5">
         <v>89</v>
@@ -3376,7 +3378,7 @@
         <v>10</v>
       </c>
       <c r="T26" s="5">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="U26" s="5">
         <v>115</v>
@@ -3388,10 +3390,10 @@
         <v>53</v>
       </c>
       <c r="X26" s="5">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Y26" s="5">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Z26" s="5">
         <v>17</v>
@@ -3406,69 +3408,69 @@
         <v>47</v>
       </c>
     </row>
-    <row r="27" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A27" s="4" t="s">
         <v>53</v>
       </c>
       <c r="B27" s="5">
-        <v>14739</v>
+        <v>14766</v>
       </c>
       <c r="C27" s="5">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="D27" s="5">
-        <v>14094</v>
+        <v>14117</v>
       </c>
       <c r="E27" s="5">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F27" s="5">
-        <v>8059</v>
+        <v>8081</v>
       </c>
       <c r="G27" s="5">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="H27" s="5">
-        <v>810</v>
+        <v>803</v>
       </c>
       <c r="I27" s="5">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="J27" s="5">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="K27" s="5">
         <v>1052</v>
       </c>
       <c r="L27" s="5">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="M27" s="5">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="N27" s="5">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O27" s="5">
         <v>253</v>
       </c>
       <c r="P27" s="5">
+        <v>47</v>
+      </c>
+      <c r="Q27" s="5">
         <v>6</v>
       </c>
-      <c r="Q27" s="5">
+      <c r="R27" s="5">
+        <v>93</v>
+      </c>
+      <c r="S27" s="5">
         <v>47</v>
-      </c>
-      <c r="R27" s="5">
-        <v>94</v>
-      </c>
-      <c r="S27" s="5">
-        <v>46</v>
       </c>
       <c r="T27" s="5">
         <v>95</v>
       </c>
       <c r="U27" s="5">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="V27" s="5">
         <v>60</v>
@@ -3477,7 +3479,7 @@
         <v>60</v>
       </c>
       <c r="X27" s="5">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Y27" s="5">
         <v>207</v>
@@ -3486,69 +3488,69 @@
         <v>31</v>
       </c>
       <c r="AA27" s="5">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="AB27" s="5">
         <v>37</v>
       </c>
       <c r="AC27" s="5">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
-    <row r="28" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A28" s="4" t="s">
         <v>54</v>
       </c>
       <c r="B28" s="5">
-        <v>32232</v>
+        <v>32252</v>
       </c>
       <c r="C28" s="5">
-        <v>648</v>
+        <v>660</v>
       </c>
       <c r="D28" s="5">
-        <v>31584</v>
+        <v>31592</v>
       </c>
       <c r="E28" s="5">
-        <v>13011</v>
+        <v>12916</v>
       </c>
       <c r="F28" s="5">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="G28" s="5">
-        <v>9367</v>
+        <v>9374</v>
       </c>
       <c r="H28" s="5">
-        <v>1011</v>
+        <v>1019</v>
       </c>
       <c r="I28" s="5">
-        <v>3417</v>
+        <v>3449</v>
       </c>
       <c r="J28" s="5">
-        <v>1183</v>
+        <v>1194</v>
       </c>
       <c r="K28" s="5">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="L28" s="5">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="M28" s="5">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="N28" s="5">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O28" s="5">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="P28" s="5">
+        <v>520</v>
+      </c>
+      <c r="Q28" s="5">
         <v>25</v>
       </c>
-      <c r="Q28" s="5">
-        <v>501</v>
-      </c>
       <c r="R28" s="5">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="S28" s="5">
         <v>27</v>
@@ -3557,10 +3559,10 @@
         <v>51</v>
       </c>
       <c r="U28" s="5">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="V28" s="5">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="W28" s="5">
         <v>16</v>
@@ -3575,72 +3577,72 @@
         <v>28</v>
       </c>
       <c r="AA28" s="5">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AB28" s="5">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="AC28" s="5">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
-    <row r="29" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A29" s="4" t="s">
         <v>55</v>
       </c>
       <c r="B29" s="5">
-        <v>9340</v>
+        <v>9413</v>
       </c>
       <c r="C29" s="5">
-        <v>708</v>
+        <v>722</v>
       </c>
       <c r="D29" s="5">
-        <v>8632</v>
+        <v>8691</v>
       </c>
       <c r="E29" s="5">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="F29" s="5">
-        <v>1119</v>
+        <v>1116</v>
       </c>
       <c r="G29" s="5">
-        <v>1686</v>
+        <v>1693</v>
       </c>
       <c r="H29" s="5">
-        <v>593</v>
+        <v>600</v>
       </c>
       <c r="I29" s="5">
-        <v>893</v>
+        <v>898</v>
       </c>
       <c r="J29" s="5">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="K29" s="5">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="L29" s="5">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="M29" s="5">
         <v>52</v>
       </c>
       <c r="N29" s="5">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="O29" s="5">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="P29" s="5">
+        <v>226</v>
+      </c>
+      <c r="Q29" s="5">
         <v>8</v>
       </c>
-      <c r="Q29" s="5">
-        <v>222</v>
-      </c>
       <c r="R29" s="5">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="S29" s="5">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="T29" s="5">
         <v>42</v>
@@ -3649,19 +3651,19 @@
         <v>177</v>
       </c>
       <c r="V29" s="5">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="W29" s="5">
         <v>34</v>
       </c>
       <c r="X29" s="5">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="Y29" s="5">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="Z29" s="5">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="AA29" s="5">
         <v>70</v>
@@ -3670,45 +3672,45 @@
         <v>37</v>
       </c>
       <c r="AC29" s="5">
-        <v>212</v>
+        <v>216</v>
       </c>
     </row>
-    <row r="30" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A30" s="4" t="s">
         <v>56</v>
       </c>
       <c r="B30" s="5">
-        <v>1865</v>
+        <v>1872</v>
       </c>
       <c r="C30" s="5">
         <v>192</v>
       </c>
       <c r="D30" s="5">
-        <v>1673</v>
+        <v>1680</v>
       </c>
       <c r="E30" s="5">
         <v>111</v>
       </c>
       <c r="F30" s="5">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G30" s="5">
         <v>162</v>
       </c>
       <c r="H30" s="5">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="I30" s="5">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J30" s="5">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="K30" s="5">
         <v>59</v>
       </c>
       <c r="L30" s="5">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="M30" s="5">
         <v>14</v>
@@ -3717,31 +3719,31 @@
         <v>46</v>
       </c>
       <c r="O30" s="5">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="P30" s="5">
+        <v>15</v>
+      </c>
+      <c r="Q30" s="5">
         <v>1</v>
-      </c>
-      <c r="Q30" s="5">
-        <v>15</v>
       </c>
       <c r="R30" s="5">
         <v>38</v>
       </c>
       <c r="S30" s="5">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="T30" s="5">
         <v>28</v>
       </c>
       <c r="U30" s="5">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="V30" s="5">
         <v>27</v>
       </c>
       <c r="W30" s="5">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="X30" s="5">
         <v>4</v>
@@ -3753,7 +3755,7 @@
         <v>4</v>
       </c>
       <c r="AA30" s="5">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AB30" s="5">
         <v>4</v>
@@ -3762,214 +3764,214 @@
         <v>16</v>
       </c>
     </row>
-    <row r="31" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A31" s="4" t="s">
         <v>57</v>
       </c>
       <c r="B31" s="5">
-        <v>15444</v>
+        <v>15495</v>
       </c>
       <c r="C31" s="5">
-        <v>1410</v>
+        <v>1416</v>
       </c>
       <c r="D31" s="5">
-        <v>14034</v>
+        <v>14079</v>
       </c>
       <c r="E31" s="5">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="F31" s="5">
-        <v>1009</v>
+        <v>1023</v>
       </c>
       <c r="G31" s="5">
-        <v>2068</v>
+        <v>2067</v>
       </c>
       <c r="H31" s="5">
-        <v>2045</v>
+        <v>2053</v>
       </c>
       <c r="I31" s="5">
         <v>1662</v>
       </c>
       <c r="J31" s="5">
-        <v>1583</v>
+        <v>1591</v>
       </c>
       <c r="K31" s="5">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="L31" s="5">
         <v>637</v>
       </c>
       <c r="M31" s="5">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="N31" s="5">
         <v>483</v>
       </c>
       <c r="O31" s="5">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="P31" s="5">
-        <v>26</v>
+        <v>133</v>
       </c>
       <c r="Q31" s="5">
-        <v>134</v>
+        <v>27</v>
       </c>
       <c r="R31" s="5">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="S31" s="5">
         <v>67</v>
       </c>
       <c r="T31" s="5">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="U31" s="5">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="V31" s="5">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="W31" s="5">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="X31" s="5">
         <v>37</v>
       </c>
       <c r="Y31" s="5">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Z31" s="5">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AA31" s="5">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AB31" s="5">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AC31" s="5">
         <v>189</v>
       </c>
     </row>
-    <row r="32" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A32" s="4" t="s">
         <v>58</v>
       </c>
       <c r="B32" s="5">
-        <v>28349</v>
+        <v>28695</v>
       </c>
       <c r="C32" s="5">
-        <v>2246</v>
+        <v>2269</v>
       </c>
       <c r="D32" s="5">
-        <v>26103</v>
+        <v>26426</v>
       </c>
       <c r="E32" s="5">
-        <v>385</v>
+        <v>396</v>
       </c>
       <c r="F32" s="5">
-        <v>7728</v>
+        <v>7740</v>
       </c>
       <c r="G32" s="5">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="H32" s="5">
-        <v>5817</v>
+        <v>6021</v>
       </c>
       <c r="I32" s="5">
-        <v>2167</v>
+        <v>2177</v>
       </c>
       <c r="J32" s="5">
-        <v>1414</v>
+        <v>1430</v>
       </c>
       <c r="K32" s="5">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="L32" s="5">
-        <v>518</v>
+        <v>532</v>
       </c>
       <c r="M32" s="5">
         <v>2717</v>
       </c>
       <c r="N32" s="5">
-        <v>753</v>
+        <v>760</v>
       </c>
       <c r="O32" s="5">
-        <v>665</v>
+        <v>672</v>
       </c>
       <c r="P32" s="5">
-        <v>283</v>
+        <v>21</v>
       </c>
       <c r="Q32" s="5">
-        <v>21</v>
+        <v>284</v>
       </c>
       <c r="R32" s="5">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="S32" s="5">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="T32" s="5">
-        <v>488</v>
+        <v>498</v>
       </c>
       <c r="U32" s="5">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="V32" s="5">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="W32" s="5">
-        <v>356</v>
+        <v>365</v>
       </c>
       <c r="X32" s="5">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="Y32" s="5">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Z32" s="5">
         <v>51</v>
       </c>
       <c r="AA32" s="5">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AB32" s="5">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AC32" s="5">
-        <v>122</v>
+        <v>127</v>
       </c>
     </row>
-    <row r="33" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:29" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A33" s="4" t="s">
         <v>59</v>
       </c>
       <c r="B33" s="5">
-        <v>2197</v>
+        <v>2198</v>
       </c>
       <c r="C33" s="5">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D33" s="5">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="E33" s="5">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F33" s="5">
         <v>274</v>
       </c>
       <c r="G33" s="5">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H33" s="5">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="I33" s="5">
         <v>112</v>
       </c>
       <c r="J33" s="5">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="K33" s="5">
         <v>185</v>
@@ -3981,16 +3983,16 @@
         <v>37</v>
       </c>
       <c r="N33" s="5">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O33" s="5">
         <v>68</v>
       </c>
       <c r="P33" s="5">
+        <v>4</v>
+      </c>
+      <c r="Q33" s="5">
         <v>2</v>
-      </c>
-      <c r="Q33" s="5">
-        <v>4</v>
       </c>
       <c r="R33" s="5">
         <v>29</v>
@@ -3999,7 +4001,7 @@
         <v>47</v>
       </c>
       <c r="T33" s="5">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="U33" s="5">
         <v>135</v>
@@ -4011,7 +4013,7 @@
         <v>12</v>
       </c>
       <c r="X33" s="5">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Y33" s="5">
         <v>66</v>
